--- a/StructureDefinition-open-elis-observation.xlsx
+++ b/StructureDefinition-open-elis-observation.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2396" uniqueCount="520">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T18:31:44+00:00</t>
+    <t>2025-09-03T10:18:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>A Observation Resource used for FHIR Exchange</t>
+    <t>An Observation Resource used for FHIR Exchange</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -1011,8 +1011,8 @@
 </t>
   </si>
   <si>
-    <t>dateTime
-PeriodTiminginstant</t>
+    <t xml:space="preserve">dateTime
+</t>
   </si>
   <si>
     <t>Clinically relevant time/time-period for observation</t>
@@ -1067,7 +1067,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Practitioner|PractitionerRole|Organization|CareTeam|Patient|RelatedPerson)
+    <t xml:space="preserve">Reference(http://digi-uw.github.io/openelis-global-ig/StructureDefinition/open-elispractitioner)
 </t>
   </si>
   <si>
@@ -1095,8 +1095,8 @@
     <t>Observation.value[x]</t>
   </si>
   <si>
-    <t>Quantity
-CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
+    <t xml:space="preserve">Quantity
+</t>
   </si>
   <si>
     <t>Actual result</t>
@@ -1598,6 +1598,10 @@
   </si>
   <si>
     <t>Observation.component.value[x]</t>
+  </si>
+  <si>
+    <t>Quantity
+CodeableConceptstringbooleanintegerRangeRatioSampledDatatimedateTimePeriod</t>
   </si>
   <si>
     <t>Actual component result</t>
@@ -8922,16 +8926,16 @@
         <v>92</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>348</v>
+        <v>508</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="M57" t="s" s="2">
         <v>350</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>352</v>
@@ -9004,7 +9008,7 @@
         <v>17</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>356</v>
@@ -9021,10 +9025,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9050,13 +9054,13 @@
         <v>188</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>363</v>
@@ -9108,7 +9112,7 @@
         <v>17</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9146,10 +9150,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9233,7 +9237,7 @@
         <v>17</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9271,10 +9275,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9300,10 +9304,10 @@
         <v>80</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>430</v>
@@ -9358,7 +9362,7 @@
         <v>17</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>

--- a/StructureDefinition-open-elis-observation.xlsx
+++ b/StructureDefinition-open-elis-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T10:18:48+00:00</t>
+    <t>2026-03-23T16:02:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -377,7 +377,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -621,7 +621,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -648,7 +648,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>https://demo.openelis-global.org/result_uuid</t>
+    <t>http://openelis-global.org/result_uuid</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -721,7 +721,7 @@
     <t>Observation.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.0.1)
 </t>
   </si>
   <si>
@@ -782,7 +782,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -861,7 +861,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode="COMP].target[classCode="LIST", moodCode="EVN"].code</t>
@@ -895,7 +895,7 @@
     <t>Codes identifying names of simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -953,7 +953,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -976,7 +976,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Encounter)
+    <t xml:space="preserve">Reference(Encounter|4.0.1)
 </t>
   </si>
   <si>
@@ -1149,7 +1149,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1181,7 +1181,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1237,7 +1237,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1270,7 +1270,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1282,7 +1282,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1313,7 +1313,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1393,7 +1393,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1443,7 +1443,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1476,7 +1476,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1513,7 +1513,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Observation|QuestionnaireResponse|MolecularSequence)
+    <t xml:space="preserve">Reference(Observation|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1535,7 +1535,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|Observation|MolecularSequence)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|Observation|4.0.1|MolecularSequence|4.0.1)
 </t>
   </si>
   <si>
@@ -1940,7 +1940,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="95.26171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="122.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1955,7 +1955,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="43.21484375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="47.7421875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/StructureDefinition-open-elis-observation.xlsx
+++ b/StructureDefinition-open-elis-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-23T16:02:58+00:00</t>
+    <t>2026-05-11T11:15:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-observation.xlsx
+++ b/StructureDefinition-open-elis-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T11:15:58+00:00</t>
+    <t>2026-05-11T15:58:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-open-elis-observation.xlsx
+++ b/StructureDefinition-open-elis-observation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:58:07+00:00</t>
+    <t>2026-05-12T16:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
